--- a/profiles/workflow/profile-crate/ro-crate-metadata.xlsx
+++ b/profiles/workflow/profile-crate/ro-crate-metadata.xlsx
@@ -16,9 +16,9 @@
     <sheet sheetId="10" name="@type=PropertyValue" state="visible" r:id="rId13"/>
     <sheet sheetId="11" name="@type=ItemList" state="visible" r:id="rId14"/>
     <sheet sheetId="12" name="@type=LearningResource" state="visible" r:id="rId15"/>
-    <sheet sheetId="13" name="@type=DigitalFormat" state="visible" r:id="rId16"/>
-    <sheet sheetId="14" name="@type=ComputerLanguage" state="visible" r:id="rId17"/>
-    <sheet sheetId="15" name="@type=DefinedTerm" state="visible" r:id="rId18"/>
+    <sheet sheetId="13" name="@type=DefinedTerm" state="visible" r:id="rId16"/>
+    <sheet sheetId="14" name="@type=DigitalFormat" state="visible" r:id="rId17"/>
+    <sheet sheetId="15" name="@type=ComputerLanguage" state="visible" r:id="rId18"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -177,6 +177,21 @@
     <t/>
   </si>
   <si>
+    <t>crate-o-mode.json</t>
+  </si>
+  <si>
+    <t>Crate-O Editor Mode File</t>
+  </si>
+  <si>
+    <t>["https://www.nationalarchives.gov.uk/PRONOM/fmt/817", application/json]</t>
+  </si>
+  <si>
+    <t>2026-05-22T08:29:17+10:00</t>
+  </si>
+  <si>
+    <t>Mini Crate-O mode file for this profile (metadata, input groups, lookup and enabled classes — the schema/grammar is provided by the MASP profile crate itself).</t>
+  </si>
+  <si>
     <t>example_workflow.cwl</t>
   </si>
   <si>
@@ -204,21 +219,6 @@
     <t>text/markdown</t>
   </si>
   <si>
-    <t>crate-o-mode.json</t>
-  </si>
-  <si>
-    <t>Crate-O Editor Mode File</t>
-  </si>
-  <si>
-    <t>["https://www.nationalarchives.gov.uk/PRONOM/fmt/817", application/json]</t>
-  </si>
-  <si>
-    <t>2026-05-22T08:29:17+10:00</t>
-  </si>
-  <si>
-    <t>Mini Crate-O mode file for this profile (metadata, input groups, lookup and enabled classes — the schema/grammar is provided by the MASP profile crate itself).</t>
-  </si>
-  <si>
     <t>#author</t>
   </si>
   <si>
@@ -765,6 +765,18 @@
     <t>["https://w3id.org/workflowhub/workflow-ro-crate#cwl", "https://w3id.org/workflowhub/workflow-ro-crate#galaxy", "https://w3id.org/workflowhub/workflow-ro-crate#knime", "https://w3id.org/workflowhub/workflow-ro-crate#nextflow", "https://w3id.org/workflowhub/workflow-ro-crate#snakemake"]</t>
   </si>
   <si>
+    <t>#conformanceIndicators</t>
+  </si>
+  <si>
+    <t>Supported conformsTo identifiers</t>
+  </si>
+  <si>
+    <t>Canonical identifiers that indicate conformance to this profile.</t>
+  </si>
+  <si>
+    <t>"https://w3id.org/ro/workflow-crate/1.0"</t>
+  </si>
+  <si>
     <t>#programmingLanguageCWLList</t>
   </si>
   <si>
@@ -774,18 +786,6 @@
     <t>A list containing only the Common Workflow Language (CWL) as a programming language for the Workflow Description.</t>
   </si>
   <si>
-    <t>#conformanceIndicators</t>
-  </si>
-  <si>
-    <t>Supported conformsTo identifiers</t>
-  </si>
-  <si>
-    <t>Canonical identifiers that indicate conformance to this profile.</t>
-  </si>
-  <si>
-    <t>"https://w3id.org/ro/workflow-crate/1.0"</t>
-  </si>
-  <si>
     <t>#WorkflowExample</t>
   </si>
   <si>
@@ -798,12 +798,36 @@
     <t>["./", "https://w3id.org/workflowhub/workflow-ro-crate/1.0", "example_workflow.cwl", "diagram.svg", "README.md"]</t>
   </si>
   <si>
+    <t>https://w3id.org/ro/mode</t>
+  </si>
+  <si>
+    <t>DefinedTerm</t>
+  </si>
+  <si>
+    <t>Editor Mode</t>
+  </si>
+  <si>
+    <t>Role indicating a resource is an editor configuration mode file.</t>
+  </si>
+  <si>
+    <t>https://w3id.org/ro/conformance-indicators</t>
+  </si>
+  <si>
+    <t>Role indicating a resource enumerates identifiers that are accepted as conformance indicators for the profile.</t>
+  </si>
+  <si>
+    <t>https://www.nationalarchives.gov.uk/PRONOM/fmt/471</t>
+  </si>
+  <si>
+    <t>DigitalFormat</t>
+  </si>
+  <si>
+    <t>Hypertext Markup Language</t>
+  </si>
+  <si>
     <t>https://www.nationalarchives.gov.uk/PRONOM/fmt/1149</t>
   </si>
   <si>
-    <t>DigitalFormat</t>
-  </si>
-  <si>
     <t>Markdown</t>
   </si>
   <si>
@@ -813,12 +837,6 @@
     <t>JSON Data Interchange Format</t>
   </si>
   <si>
-    <t>https://www.nationalarchives.gov.uk/PRONOM/fmt/471</t>
-  </si>
-  <si>
-    <t>Hypertext Markup Language</t>
-  </si>
-  <si>
     <t>alternateName</t>
   </si>
   <si>
@@ -877,24 +895,6 @@
   </si>
   <si>
     <t>"https://snakemake.readthedocs.io"</t>
-  </si>
-  <si>
-    <t>https://w3id.org/ro/mode</t>
-  </si>
-  <si>
-    <t>DefinedTerm</t>
-  </si>
-  <si>
-    <t>Editor Mode</t>
-  </si>
-  <si>
-    <t>Role indicating a resource is an editor configuration mode file.</t>
-  </si>
-  <si>
-    <t>https://w3id.org/ro/conformance-indicators</t>
-  </si>
-  <si>
-    <t>Role indicating a resource enumerates identifiers that are accepted as conformance indicators for the profile.</t>
   </si>
 </sst>
 </file>
@@ -1494,7 +1494,7 @@
         <v>228</v>
       </c>
       <c r="E5" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -1628,24 +1628,24 @@
         <v>248</v>
       </c>
       <c r="E4" t="s">
-        <v>52</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B5" t="s">
         <v>239</v>
       </c>
       <c r="C5" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D5" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E5" t="s">
-        <v>252</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1704,6 +1704,62 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="4" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C2" t="s">
+        <v>259</v>
+      </c>
+      <c r="D2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>261</v>
+      </c>
+      <c r="B3" t="s">
+        <v>258</v>
+      </c>
+      <c r="C3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -1723,35 +1779,35 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="B2" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="C2" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B3" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="C3" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="B4" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="C4" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
     </row>
   </sheetData>
@@ -1760,7 +1816,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -1779,10 +1835,10 @@
         <v>6</v>
       </c>
       <c r="D1" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="E1" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="F1" t="s">
         <v>67</v>
@@ -1790,145 +1846,89 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="B2" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="C2" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="D2" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="E2" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="F2" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="B3" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="C3" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="E3" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="F3" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="B4" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="C4" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="E4" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="F4" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B5" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="C5" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="E5" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="F5" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="B6" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="C6" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="E6" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="F6" t="s">
-        <v>283</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="4" width="20" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>284</v>
-      </c>
-      <c r="B2" t="s">
-        <v>285</v>
-      </c>
-      <c r="C2" t="s">
-        <v>286</v>
-      </c>
-      <c r="D2" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>288</v>
-      </c>
-      <c r="B3" t="s">
-        <v>285</v>
-      </c>
-      <c r="C3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D3" t="s">
         <v>289</v>
       </c>
     </row>
@@ -2119,66 +2119,66 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>50</v>
       </c>
       <c r="B4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" t="s">
         <v>51</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F4" t="s">
+        <v>53</v>
+      </c>
+      <c r="G4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" t="s">
         <v>28</v>
       </c>
-      <c r="I4" t="s">
-        <v>52</v>
-      </c>
-      <c r="J4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I5" t="s">
+        <v>57</v>
+      </c>
+      <c r="J5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B6" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+      <c r="C6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B7" t="s">
         <v>42</v>
       </c>
-      <c r="C7" t="s">
-        <v>60</v>
-      </c>
       <c r="D7" t="s">
-        <v>61</v>
-      </c>
-      <c r="F7" t="s">
-        <v>62</v>
-      </c>
-      <c r="G7" t="s">
         <v>63</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
